--- a/jpcore-r4/develop/ValueSet-jp-documentcodes-diagnosticreport-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-documentcodes-diagnosticreport-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>微生物学的検査報告書</t>
+  </si>
+  <si>
+    <t>32453-3</t>
+  </si>
+  <si>
+    <t>口腔診査報告書</t>
   </si>
   <si>
     <t/>
@@ -575,7 +581,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -859,15 +865,23 @@
         <v>96</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/develop/ValueSet-jp-documentcodes-diagnosticreport-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-documentcodes-diagnosticreport-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/ValueSet-jp-documentcodes-diagnosticreport-vs.xlsx
+++ b/jpcore-r4/develop/ValueSet-jp-documentcodes-diagnosticreport-vs.xlsx
@@ -93,7 +93,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright JED-Project、JAHIS、日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG  
+This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995+, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
     <t>Immutable</t>
